--- a/real_host_hotspots.xlsx
+++ b/real_host_hotspots.xlsx
@@ -520,10 +520,10 @@
         <v>2.666666666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>2.981423969999719</v>
+        <v>2.98142396999972</v>
       </c>
       <c r="F3" t="n">
-        <v>5.648090636666385</v>
+        <v>5.648090636666386</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>266835,</t>
+          <t>224911,</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>['266835.01', '266835.02', '266835.03', '266835.04']</t>
+          <t>['224911.01', '224911.02', '224911.03', '224911.04']</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>224911,</t>
+          <t>266835,</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>['224911.01', '224911.02', '224911.03', '224911.04']</t>
+          <t>['266835.01', '266835.02', '266835.03', '266835.04']</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7955,</t>
+          <t>220668,</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>['7955.01', '7955.02', '7955.03']</t>
+          <t>['220668.01', '220668.02', '220668.03']</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>220668,</t>
+          <t>7955,</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -943,7 +943,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>['220668.01', '220668.02', '220668.03']</t>
+          <t>['7955.01', '7955.02', '7955.03']</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -958,11 +958,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100226,</t>
+          <t>10090,</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>1.62962962962963</v>
@@ -975,11 +975,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>['100226.01', '100226.02', '100226.03', '100226.04', '100226.05', '100226.06']</t>
+          <t>['10090.01', '10090.02', '10090.03']</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -990,11 +990,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10090,</t>
+          <t>100226,</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>1.62962962962963</v>
@@ -1007,11 +1007,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>['10090.01', '10090.02', '10090.03']</t>
+          <t>['100226.01', '100226.02', '100226.03', '100226.04', '100226.05', '100226.06']</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>h020,</t>
+          <t>h003,</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>['h020-001', 'h020-002']</t>
+          <t>['h003-001', 'h003-002']</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>h018,</t>
+          <t>h020,</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>['h018-001', 'h018-002']</t>
+          <t>['h020-001', 'h020-002']</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>h016,</t>
+          <t>h018,</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>['h016-001', 'h016-002']</t>
+          <t>['h018-001', 'h018-002']</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>h003,</t>
+          <t>h008,</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>['h003-001', 'h003-002']</t>
+          <t>['h008-001', 'h008-002']</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>h008,</t>
+          <t>h016,</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>['h008-001', 'h008-002']</t>
+          <t>['h016-001', 'h016-002']</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>h000,</t>
+          <t>h002,</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>['h000-001', 'h000-002']</t>
+          <t>['h002-001', 'h002-002']</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>h002,</t>
+          <t>h000,</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>['h002-001', 'h002-002']</t>
+          <t>['h000-001', 'h000-002']</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>h013,</t>
+          <t>h001,</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>['h013-001', 'h013-002']</t>
+          <t>['h001-001', 'h001-002']</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1310,11 +1310,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>h010,</t>
+          <t>h024,</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>1.272727272727273</v>
@@ -1327,11 +1327,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>['h010-001', 'h010-002', 'h010-003']</t>
+          <t>['h024-001', 'h024-002', 'h024-003', 'h024-004']</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>h001,</t>
+          <t>h000,</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>['h001-001', 'h001-002']</t>
+          <t>['h000-001', 'h000-002']</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>h000,</t>
+          <t>h011,</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>['h000-001', 'h000-002']</t>
+          <t>['h011-001', 'h011-002']</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1406,11 +1406,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>h024,</t>
+          <t>h010,</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>1.272727272727273</v>
@@ -1423,11 +1423,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>['h024-001', 'h024-002', 'h024-003', 'h024-004']</t>
+          <t>['h010-001', 'h010-002', 'h010-003']</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>h011,</t>
+          <t>h013,</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>['h011-001', 'h011-002']</t>
+          <t>['h013-001', 'h013-002']</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>h006,</t>
+          <t>h004,</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>['h006-001', 'h006-002']</t>
+          <t>['h004-001', 'h004-002']</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>h004,</t>
+          <t>h007,</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>['h004-001', 'h004-002']</t>
+          <t>['h007-001', 'h007-002']</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>h007,</t>
+          <t>h006,</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>['h007-001', 'h007-002']</t>
+          <t>['h006-001', 'h006-002']</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -1672,7 +1672,7 @@
         <v>1.066666666666667</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2494438257849294</v>
+        <v>0.2494438257849295</v>
       </c>
       <c r="F39" t="n">
         <v>1.316110492451596</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>h018,</t>
+          <t>h009,</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>['h018-001', 'h018-002', 'h018-003', 'h018-004', 'h018-005', 'h018-006']</t>
+          <t>['h009-001', 'h009-002', 'h009-003', 'h009-004', 'h009-005', 'h009-006']</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>h009,</t>
+          <t>h018,</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>['h009-001', 'h009-002', 'h009-003', 'h009-004', 'h009-005', 'h009-006']</t>
+          <t>['h018-001', 'h018-002', 'h018-003', 'h018-004', 'h018-005', 'h018-006']</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -1800,7 +1800,7 @@
         <v>1.066666666666667</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2494438257849294</v>
+        <v>0.2494438257849295</v>
       </c>
       <c r="F43" t="n">
         <v>1.316110492451596</v>
@@ -1992,10 +1992,10 @@
         <v>1.142857142857143</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3499271061118827</v>
+        <v>0.3499271061118826</v>
       </c>
       <c r="F49" t="n">
-        <v>1.492784248969026</v>
+        <v>1.492784248969025</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
